--- a/outputs/monitor_xlsx/20260312.xlsx
+++ b/outputs/monitor_xlsx/20260312.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2325,6 +2325,112 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6330</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>719</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-536</v>
+      </c>
+      <c r="H23" t="n">
+        <v>66</v>
+      </c>
+      <c r="I23" t="n">
+        <v>442</v>
+      </c>
+      <c r="J23" t="n">
+        <v>39</v>
+      </c>
+      <c r="K23" t="n">
+        <v>245</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1261</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8964</v>
+      </c>
+      <c r="N23" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1495</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2224</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1042</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>202</v>
+      </c>
+      <c r="J24" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2994</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15766</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106265</v>
+      </c>
+      <c r="N24" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/outputs/monitor_xlsx/20260312.xlsx
+++ b/outputs/monitor_xlsx/20260312.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>33581.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+1.47%</t>
-        </is>
-      </c>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5120.8$</t>
+          <t>311.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.90%</t>
-        </is>
-      </c>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7643.17</t>
+          <t>4.27%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.43%</t>
-        </is>
-      </c>
+          <t>+1.47%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>5115.8$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+12.63%</t>
-        </is>
-      </c>
+          <t>-1.00%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>95.89$</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+9.90%</t>
-        </is>
-      </c>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-711.28億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-430.17億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-2150.86億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-161.45億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3228.97億</t>
-        </is>
-      </c>
+          <t>7643.17</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-3.43%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-7.52億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>74.11億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>370.56億</t>
-        </is>
-      </c>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+12.63%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>144.16%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>134.77%</t>
-        </is>
-      </c>
+          <t>95.73$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+9.72%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +761,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-810.77億</t>
+          <t>-711.28億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-513.66億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2568.32億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,54 +799,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12602口</t>
-        </is>
-      </c>
+          <t>-7.52億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13971口</t>
-        </is>
-      </c>
+          <t>88.8億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>444.0億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-810.77億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12602口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>13971口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-37.33億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-8.54億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-42.69億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-6.85億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-136.94億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -860,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-430.17億</t>
+          <t>-513.66億</t>
         </is>
       </c>
     </row>
@@ -872,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2150.86億</t>
+          <t>-2568.32億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-161.45億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3228.97億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>74.11億</t>
+          <t>88.8億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370.56億</t>
+          <t>444.0億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-6.85億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-136.94億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -994,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>134.77%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1316,13 @@
         <v>-76390</v>
       </c>
       <c r="H4" t="n">
-        <v>-408035</v>
+        <v>-331136</v>
       </c>
       <c r="I4" t="n">
         <v>1300</v>
       </c>
       <c r="J4" t="n">
-        <v>17415</v>
+        <v>15115</v>
       </c>
       <c r="K4" t="n">
         <v>16039</v>
@@ -1218,20 +1331,12 @@
         <v>13356</v>
       </c>
       <c r="M4" t="n">
-        <v>63642</v>
+        <v>52498</v>
       </c>
       <c r="N4" t="n">
         <v>-4437710</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1240,41 +1345,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>922</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2770</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-37</v>
+        <v>-263</v>
       </c>
       <c r="H5" t="n">
-        <v>-408</v>
+        <v>-1349</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-62</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-654</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
-        <v>9355</v>
+        <v>2800</v>
       </c>
       <c r="M5" t="n">
-        <v>48696</v>
+        <v>11221</v>
       </c>
       <c r="N5" t="n">
-        <v>-26182</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78820</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1283,12 +1400,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1297,47 +1414,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>922</v>
+        <v>1370</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-1.07</v>
+        <v>-2.14</v>
       </c>
       <c r="F6" t="n">
-        <v>2770</v>
+        <v>7808</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-263</v>
+        <v>-593</v>
       </c>
       <c r="H6" t="n">
-        <v>-1640</v>
+        <v>-91</v>
       </c>
       <c r="I6" t="n">
-        <v>-62</v>
+        <v>-17</v>
       </c>
       <c r="J6" t="n">
-        <v>-562</v>
+        <v>1526</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="L6" t="n">
-        <v>2800</v>
+        <v>5954</v>
       </c>
       <c r="M6" t="n">
-        <v>13998</v>
+        <v>23236</v>
       </c>
       <c r="N6" t="n">
-        <v>-78820</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648981</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1346,12 +1455,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1360,47 +1469,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1370</v>
+        <v>1885</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-2.14</v>
+        <v>-2.84</v>
       </c>
       <c r="F7" t="n">
-        <v>7808</v>
+        <v>40662</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-593</v>
+        <v>-19046</v>
       </c>
       <c r="H7" t="n">
-        <v>-1596</v>
+        <v>-44706</v>
       </c>
       <c r="I7" t="n">
-        <v>-17</v>
+        <v>283</v>
       </c>
       <c r="J7" t="n">
-        <v>2319</v>
+        <v>4093</v>
       </c>
       <c r="K7" t="n">
-        <v>241</v>
+        <v>624</v>
       </c>
       <c r="L7" t="n">
-        <v>5954</v>
+        <v>25171</v>
       </c>
       <c r="M7" t="n">
-        <v>28968</v>
+        <v>97486</v>
       </c>
       <c r="N7" t="n">
-        <v>-648981</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6483131</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1409,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1885</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-2.84</v>
+        <v>1505</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1.35</v>
       </c>
       <c r="F8" t="n">
-        <v>40662</v>
+        <v>4026</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-19046</v>
+        <v>-67</v>
       </c>
       <c r="H8" t="n">
-        <v>-54461</v>
+        <v>-746</v>
       </c>
       <c r="I8" t="n">
-        <v>283</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
-        <v>5587</v>
+        <v>789</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>92</v>
       </c>
       <c r="L8" t="n">
-        <v>25171</v>
+        <v>1875</v>
       </c>
       <c r="M8" t="n">
-        <v>120439</v>
+        <v>7250</v>
       </c>
       <c r="N8" t="n">
-        <v>-6483131</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140169</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1472,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>109</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-4.39</v>
+        <v>1495</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>167667</v>
+        <v>2224</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>12768</v>
+        <v>83</v>
       </c>
       <c r="H9" t="n">
-        <v>-22179</v>
+        <v>959</v>
       </c>
       <c r="I9" t="n">
-        <v>-1137</v>
+        <v>-3</v>
       </c>
       <c r="J9" t="n">
-        <v>-2697</v>
+        <v>205</v>
       </c>
       <c r="K9" t="n">
-        <v>4780</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>128070</v>
+        <v>2994</v>
       </c>
       <c r="M9" t="n">
-        <v>631125</v>
+        <v>12772</v>
       </c>
       <c r="N9" t="n">
-        <v>-1114597</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106265</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1561,13 +1646,13 @@
         <v>-274</v>
       </c>
       <c r="H10" t="n">
-        <v>-2048</v>
+        <v>-1286</v>
       </c>
       <c r="I10" t="n">
         <v>324</v>
       </c>
       <c r="J10" t="n">
-        <v>1447</v>
+        <v>789</v>
       </c>
       <c r="K10" t="n">
         <v>181</v>
@@ -1576,20 +1661,12 @@
         <v>1967</v>
       </c>
       <c r="M10" t="n">
-        <v>9007</v>
+        <v>7179</v>
       </c>
       <c r="N10" t="n">
         <v>-89475</v>
       </c>
-      <c r="O10" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1598,12 +1675,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1612,47 +1689,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3315</v>
+        <v>1690</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-1.49</v>
+        <v>-6.63</v>
       </c>
       <c r="F11" t="n">
-        <v>1580</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>78</v>
+        <v>1042</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-42</v>
       </c>
       <c r="H11" t="n">
-        <v>104</v>
+        <v>475</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>-22</v>
+        <v>-290</v>
       </c>
       <c r="K11" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L11" t="n">
-        <v>5832</v>
+        <v>4426</v>
       </c>
       <c r="M11" t="n">
-        <v>29879</v>
+        <v>18352</v>
       </c>
       <c r="N11" t="n">
-        <v>-19722</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19312</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1661,12 +1730,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1675,47 +1744,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1690</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>-6.63</v>
+        <v>6330</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>7.29</v>
       </c>
       <c r="F12" t="n">
-        <v>1042</v>
+        <v>719</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>-42</v>
+        <v>-100</v>
       </c>
       <c r="H12" t="n">
-        <v>-123</v>
+        <v>-436</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="J12" t="n">
-        <v>-346</v>
+        <v>376</v>
       </c>
       <c r="K12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>4426</v>
+        <v>245</v>
       </c>
       <c r="M12" t="n">
-        <v>22923</v>
+        <v>1016</v>
       </c>
       <c r="N12" t="n">
-        <v>-19312</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8964</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1738,25 +1799,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-7.4</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>860</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-42</v>
       </c>
       <c r="H13" t="n">
-        <v>-3116</v>
+        <v>-1999</v>
       </c>
       <c r="I13" t="n">
         <v>-105</v>
       </c>
       <c r="J13" t="n">
-        <v>2176</v>
+        <v>2030</v>
       </c>
       <c r="K13" t="n">
         <v>261</v>
@@ -1765,20 +1826,12 @@
         <v>-260</v>
       </c>
       <c r="M13" t="n">
-        <v>296</v>
+        <v>164</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1787,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1801,44 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-1.85</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>927</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>-31</v>
+        <v>-117</v>
       </c>
       <c r="H14" t="n">
-        <v>672</v>
+        <v>-99</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-560</v>
       </c>
       <c r="J14" t="n">
-        <v>-501</v>
+        <v>-214</v>
       </c>
       <c r="K14" t="n">
-        <v>-38</v>
+        <v>-4</v>
       </c>
       <c r="L14" t="n">
-        <v>-16</v>
+        <v>-257</v>
       </c>
       <c r="M14" t="n">
-        <v>-215</v>
+        <v>-123</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1847,12 +1895,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1861,47 +1909,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>387.5</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.04</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>3953</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-117</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>242</v>
       </c>
       <c r="H15" t="n">
-        <v>-144</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-560</v>
+        <v>-346</v>
       </c>
       <c r="J15" t="n">
-        <v>-1853</v>
+        <v>144</v>
       </c>
       <c r="K15" t="n">
-        <v>-4</v>
+        <v>52</v>
       </c>
       <c r="L15" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="M15" t="n">
-        <v>249</v>
+        <v>-266</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1910,12 +1947,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1924,510 +1961,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>6.72</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1084</v>
+        <v>904</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>-773</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>-75</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>-7</v>
+        <v>13</v>
       </c>
       <c r="L16" t="n">
-        <v>-46</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>-67</v>
+        <v>104</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>185</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F17" t="n">
-        <v>9096</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-668</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-927</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>79</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4305</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20855</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-11176</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4026</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-67</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-149</v>
-      </c>
-      <c r="I18" t="n">
-        <v>53</v>
-      </c>
-      <c r="J18" t="n">
-        <v>727</v>
-      </c>
-      <c r="K18" t="n">
-        <v>92</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1875</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9065</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-140169</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>841</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2587</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>276</v>
-      </c>
-      <c r="I19" t="n">
-        <v>43</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>166</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-379</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-553</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1972</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>-155</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-416</v>
-      </c>
-      <c r="I20" t="n">
-        <v>41</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1102</v>
-      </c>
-      <c r="K20" t="n">
-        <v>83</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1965</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10319</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-47605</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>962</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G21" t="n">
-        <v>145</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>13</v>
-      </c>
-      <c r="K21" t="n">
-        <v>35</v>
-      </c>
-      <c r="L21" t="n">
-        <v>139</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>278</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9272</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>622</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1525</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-18</v>
-      </c>
-      <c r="J22" t="n">
-        <v>119</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8268</v>
-      </c>
-      <c r="L22" t="n">
-        <v>36422</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-58819</v>
-      </c>
-      <c r="N22" t="n">
-        <v>28.05</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>6330</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="E23" t="n">
-        <v>719</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-536</v>
-      </c>
-      <c r="H23" t="n">
-        <v>66</v>
-      </c>
-      <c r="I23" t="n">
-        <v>442</v>
-      </c>
-      <c r="J23" t="n">
-        <v>39</v>
-      </c>
-      <c r="K23" t="n">
-        <v>245</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1261</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8964</v>
-      </c>
-      <c r="N23" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1495</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2224</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1042</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>202</v>
-      </c>
-      <c r="J24" t="n">
-        <v>22</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2994</v>
-      </c>
-      <c r="L24" t="n">
-        <v>15766</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106265</v>
-      </c>
-      <c r="N24" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260312.xlsx
+++ b/outputs/monitor_xlsx/20260312.xlsx
@@ -544,10 +544,6 @@
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.03%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+1.47%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-1.00%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.11%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-3.43%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+12.63%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+9.72%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-711.28億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-513.66億</t>
@@ -807,7 +769,6 @@
           <t>-7.52億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>88.8億</t>
@@ -818,8 +779,6 @@
           <t>444.0億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-810.77億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>12602口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13971口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-37.33億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-8.54億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1994,6 +1937,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>355</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1197</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2036</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>407</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7859</v>
+      </c>
+      <c r="L17" t="n">
+        <v>35507</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260312.xlsx
+++ b/outputs/monitor_xlsx/20260312.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-2.05</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>131518</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-76390</v>
       </c>
       <c r="H4" t="n">
-        <v>-331136</v>
+        <v>-407526</v>
       </c>
       <c r="I4" t="n">
         <v>1300</v>
       </c>
       <c r="J4" t="n">
-        <v>15115</v>
+        <v>16415</v>
       </c>
       <c r="K4" t="n">
         <v>16039</v>
@@ -1274,11 +1273,14 @@
         <v>13356</v>
       </c>
       <c r="M4" t="n">
-        <v>52498</v>
+        <v>65854</v>
       </c>
       <c r="N4" t="n">
         <v>-4437710</v>
       </c>
+      <c r="O4" t="n">
+        <v>0.26</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>922</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-1.07</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2770</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-263</v>
       </c>
       <c r="H5" t="n">
-        <v>-1349</v>
+        <v>-1611</v>
       </c>
       <c r="I5" t="n">
         <v>-62</v>
       </c>
       <c r="J5" t="n">
-        <v>-654</v>
+        <v>-716</v>
       </c>
       <c r="K5" t="n">
         <v>42</v>
@@ -1329,11 +1331,14 @@
         <v>2800</v>
       </c>
       <c r="M5" t="n">
-        <v>11221</v>
+        <v>14021</v>
       </c>
       <c r="N5" t="n">
         <v>-78820</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.76</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1370</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-2.14</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>7808</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-593</v>
       </c>
       <c r="H6" t="n">
-        <v>-91</v>
+        <v>-684</v>
       </c>
       <c r="I6" t="n">
         <v>-17</v>
       </c>
       <c r="J6" t="n">
-        <v>1526</v>
+        <v>1509</v>
       </c>
       <c r="K6" t="n">
         <v>241</v>
@@ -1384,11 +1389,14 @@
         <v>5954</v>
       </c>
       <c r="M6" t="n">
-        <v>23236</v>
+        <v>29190</v>
       </c>
       <c r="N6" t="n">
         <v>-648981</v>
       </c>
+      <c r="O6" t="n">
+        <v>5.91</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1885</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-2.84</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>40662</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-19046</v>
       </c>
       <c r="H7" t="n">
-        <v>-44706</v>
+        <v>-63752</v>
       </c>
       <c r="I7" t="n">
         <v>283</v>
       </c>
       <c r="J7" t="n">
-        <v>4093</v>
+        <v>4376</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -1439,11 +1447,14 @@
         <v>25171</v>
       </c>
       <c r="M7" t="n">
-        <v>97486</v>
+        <v>122657</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
+      <c r="O7" t="n">
+        <v>0.09</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1505</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1.35</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4026</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-67</v>
       </c>
       <c r="H8" t="n">
-        <v>-746</v>
+        <v>-812</v>
       </c>
       <c r="I8" t="n">
         <v>53</v>
       </c>
       <c r="J8" t="n">
-        <v>789</v>
+        <v>842</v>
       </c>
       <c r="K8" t="n">
         <v>92</v>
@@ -1494,11 +1505,14 @@
         <v>1875</v>
       </c>
       <c r="M8" t="n">
-        <v>7250</v>
+        <v>9125</v>
       </c>
       <c r="N8" t="n">
         <v>-140169</v>
       </c>
+      <c r="O8" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1527,20 +1541,20 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>2224</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H9" t="n">
-        <v>959</v>
+        <v>1042</v>
       </c>
       <c r="I9" t="n">
         <v>-3</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K9" t="n">
         <v>22</v>
@@ -1549,11 +1563,14 @@
         <v>2994</v>
       </c>
       <c r="M9" t="n">
-        <v>12772</v>
+        <v>15766</v>
       </c>
       <c r="N9" t="n">
         <v>-106265</v>
       </c>
+      <c r="O9" t="n">
+        <v>20.73</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2600</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>6.12</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>5442</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-274</v>
       </c>
       <c r="H10" t="n">
-        <v>-1286</v>
+        <v>-1560</v>
       </c>
       <c r="I10" t="n">
         <v>324</v>
       </c>
       <c r="J10" t="n">
-        <v>789</v>
+        <v>1113</v>
       </c>
       <c r="K10" t="n">
         <v>181</v>
@@ -1604,11 +1621,14 @@
         <v>1967</v>
       </c>
       <c r="M10" t="n">
-        <v>7179</v>
+        <v>9146</v>
       </c>
       <c r="N10" t="n">
         <v>-89475</v>
       </c>
+      <c r="O10" t="n">
+        <v>16.31</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1690</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-6.63</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>1042</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-42</v>
       </c>
       <c r="H11" t="n">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>-290</v>
+        <v>-279</v>
       </c>
       <c r="K11" t="n">
         <v>49</v>
@@ -1659,11 +1679,14 @@
         <v>4426</v>
       </c>
       <c r="M11" t="n">
-        <v>18352</v>
+        <v>22778</v>
       </c>
       <c r="N11" t="n">
         <v>-19312</v>
       </c>
+      <c r="O11" t="n">
+        <v>-12.88</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>6330</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>7.29</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>719</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-100</v>
       </c>
       <c r="H12" t="n">
-        <v>-436</v>
+        <v>-536</v>
       </c>
       <c r="I12" t="n">
         <v>66</v>
       </c>
       <c r="J12" t="n">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="K12" t="n">
         <v>39</v>
@@ -1714,11 +1737,14 @@
         <v>245</v>
       </c>
       <c r="M12" t="n">
-        <v>1016</v>
+        <v>1261</v>
       </c>
       <c r="N12" t="n">
         <v>-8964</v>
       </c>
+      <c r="O12" t="n">
+        <v>28.02</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-42</v>
       </c>
       <c r="H13" t="n">
-        <v>-1999</v>
+        <v>-2041</v>
       </c>
       <c r="I13" t="n">
         <v>-105</v>
       </c>
       <c r="J13" t="n">
-        <v>2030</v>
+        <v>1925</v>
       </c>
       <c r="K13" t="n">
         <v>261</v>
@@ -1769,11 +1795,14 @@
         <v>-260</v>
       </c>
       <c r="M13" t="n">
-        <v>164</v>
+        <v>-96</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-117</v>
       </c>
       <c r="H14" t="n">
-        <v>-99</v>
+        <v>-216</v>
       </c>
       <c r="I14" t="n">
         <v>-560</v>
       </c>
       <c r="J14" t="n">
-        <v>-214</v>
+        <v>-774</v>
       </c>
       <c r="K14" t="n">
         <v>-4</v>
@@ -1824,11 +1853,14 @@
         <v>-257</v>
       </c>
       <c r="M14" t="n">
-        <v>-123</v>
+        <v>-380</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1851,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>242</v>
       </c>
       <c r="H15" t="n">
-        <v>-346</v>
+        <v>-104</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>144</v>
@@ -1876,11 +1911,14 @@
         <v>-223</v>
       </c>
       <c r="M15" t="n">
-        <v>-266</v>
+        <v>-489</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1903,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>128</v>
+        <v>145</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>10</v>
@@ -1928,11 +1969,14 @@
         <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>355</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>9.91</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1197</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-118</v>
       </c>
-      <c r="G17" t="n">
-        <v>-2036</v>
-      </c>
       <c r="H17" t="n">
+        <v>-2131</v>
+      </c>
+      <c r="I17" t="n">
         <v>-18</v>
       </c>
-      <c r="I17" t="n">
-        <v>407</v>
-      </c>
       <c r="J17" t="n">
+        <v>550</v>
+      </c>
+      <c r="K17" t="n">
         <v>19</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7859</v>
       </c>
-      <c r="L17" t="n">
-        <v>35507</v>
-      </c>
       <c r="M17" t="n">
+        <v>35897</v>
+      </c>
+      <c r="N17" t="n">
         <v>-22001</v>
       </c>
-      <c r="N17" t="n">
-        <v>20.84</v>
+      <c r="O17" t="n">
+        <v>29.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260312.xlsx
+++ b/outputs/monitor_xlsx/20260312.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>29.14</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1785</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6611</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-730</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-5499</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-283</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-59</v>
+      </c>
+      <c r="K18" t="n">
+        <v>223</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5869</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28940</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400932</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>480</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15311</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>4701</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-490</v>
+      </c>
+      <c r="K19" t="n">
+        <v>573</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35805</v>
+      </c>
+      <c r="M19" t="n">
+        <v>186569</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392414</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>468.5</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1928</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1149</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-173</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>240</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8675</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45644</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161536</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
